--- a/papers/comparison/sota_comparison.xlsx
+++ b/papers/comparison/sota_comparison.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1abdca93598a4eb/Documents/SP Jain/3. Year 3/Semester 6/2. Computer Vision/Group Project/NeurIPS/vlm-radiology-report-gen/papers/comparison/"/>
@@ -10,14 +10,14 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="45" documentId="8_{5B46B6A8-1E60-4B80-B9CE-9D755717CFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E5A1B38-4D18-488C-A6F0-D26BE29EF9AE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C70C6920-420A-4A88-B1CF-07D11769BF00}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{C70C6920-420A-4A88-B1CF-07D11769BF00}"/>
   </bookViews>
   <sheets>
     <sheet name="iu-xray" sheetId="1" r:id="rId1"/>
     <sheet name="mimic-cxr" sheetId="2" r:id="rId2"/>
     <sheet name="cross-dataset" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,226 +51,226 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="88">
   <si>
+    <t>Method</t>
+  </si>
+  <si>
     <t>Year</t>
   </si>
   <si>
     <t>BLEU-4</t>
   </si>
   <si>
+    <t>METEOR</t>
+  </si>
+  <si>
     <t>ROUGE-L</t>
   </si>
   <si>
-    <t>METEOR</t>
+    <t>CIDEr</t>
   </si>
   <si>
     <t>BERTScore</t>
   </si>
   <si>
+    <t>Clinical Metric</t>
+  </si>
+  <si>
+    <t>CoAttention</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>KERP</t>
+  </si>
+  <si>
+    <t>R2Gen</t>
+  </si>
+  <si>
+    <t>CheXpert F1</t>
+  </si>
+  <si>
+    <t>CMM + RL</t>
+  </si>
+  <si>
+    <t>Human eval improved</t>
+  </si>
+  <si>
+    <t>MPO</t>
+  </si>
+  <si>
+    <t>Preference optimization</t>
+  </si>
+  <si>
+    <t>HDGAN</t>
+  </si>
+  <si>
+    <t>X-RGen</t>
+  </si>
+  <si>
+    <t>Cross-region learning</t>
+  </si>
+  <si>
+    <t>HistGen</t>
+  </si>
+  <si>
+    <t>Histopathology reports</t>
+  </si>
+  <si>
+    <t>MediVLM</t>
+  </si>
+  <si>
+    <t>Severity scoring</t>
+  </si>
+  <si>
+    <t>HKRG</t>
+  </si>
+  <si>
+    <t>Hierarchical knowledge</t>
+  </si>
+  <si>
+    <t>RIHA</t>
+  </si>
+  <si>
+    <t>Clinical F1 0.375</t>
+  </si>
+  <si>
+    <t>KERM</t>
+  </si>
+  <si>
+    <t>Hallucination mitigation</t>
+  </si>
+  <si>
+    <t>CheXpert F1 0.276</t>
+  </si>
+  <si>
+    <t>CheXpert F1 0.292</t>
+  </si>
+  <si>
+    <t>R2GenGPT</t>
+  </si>
+  <si>
+    <t>Clinical F1 0.389</t>
+  </si>
+  <si>
+    <t>F1 0.353</t>
+  </si>
+  <si>
+    <t>GAN + RL</t>
+  </si>
+  <si>
+    <t>GIT-CXR</t>
+  </si>
+  <si>
+    <t>F1-micro 0.534</t>
+  </si>
+  <si>
+    <t>CLIP-ViT + ClinicalBERT</t>
+  </si>
+  <si>
+    <t>META-CXR</t>
+  </si>
+  <si>
+    <t>Clinical F1 0.428</t>
+  </si>
+  <si>
+    <t>Clinical F1 0.339</t>
+  </si>
+  <si>
+    <t>RaDialog</t>
+  </si>
+  <si>
+    <t>Clinical efficacy 39.7</t>
+  </si>
+  <si>
+    <t>Flamingo-CXR</t>
+  </si>
+  <si>
+    <t>CheXpert F1 0.519</t>
+  </si>
+  <si>
+    <t>SDLS</t>
+  </si>
+  <si>
+    <t>Hallucination ↓ 37.3%</t>
+  </si>
+  <si>
+    <t>Clinical F1 0.415</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Main Contribution</t>
+  </si>
+  <si>
+    <t>Key Result</t>
+  </si>
+  <si>
+    <t>MedCLIP</t>
+  </si>
+  <si>
+    <t>CheXpert / MIMIC</t>
+  </si>
+  <si>
+    <t>Contrastive medical VLM</t>
+  </si>
+  <si>
+    <t>59.4% zero-shot accuracy</t>
+  </si>
+  <si>
+    <t>BioViL</t>
+  </si>
+  <si>
+    <t>MIMIC-CXR</t>
+  </si>
+  <si>
+    <t>Biomedical vision-language alignment</t>
+  </si>
+  <si>
+    <t>Improved phrase grounding</t>
+  </si>
+  <si>
+    <t>BLIP</t>
+  </si>
+  <si>
+    <t>COCO / Web-scale</t>
+  </si>
+  <si>
+    <t>Unified VLP framework</t>
+  </si>
+  <si>
+    <t>CIDEr 129.7</t>
+  </si>
+  <si>
+    <t>CLIP</t>
+  </si>
+  <si>
+    <t>Web-scale</t>
+  </si>
+  <si>
+    <t>Contrastive image-text learning</t>
+  </si>
+  <si>
+    <t>76.2% ImageNet zero-shot</t>
+  </si>
+  <si>
+    <t>ClinicalBERT</t>
+  </si>
+  <si>
+    <t>MIMIC-III</t>
+  </si>
+  <si>
+    <t>Clinical text understanding</t>
+  </si>
+  <si>
+    <t>AUROC 0.714</t>
+  </si>
+  <si>
     <t>CheXNet</t>
   </si>
   <si>
     <t>ChestX-ray14</t>
-  </si>
-  <si>
-    <t>KERP</t>
-  </si>
-  <si>
-    <t>R2Gen</t>
-  </si>
-  <si>
-    <t>MIMIC-CXR</t>
-  </si>
-  <si>
-    <t>CheXpert F1 0.276</t>
-  </si>
-  <si>
-    <t>MedCLIP</t>
-  </si>
-  <si>
-    <t>CMM + RL</t>
-  </si>
-  <si>
-    <t>CheXpert F1 0.292</t>
-  </si>
-  <si>
-    <t>R2GenGPT</t>
-  </si>
-  <si>
-    <t>Clinical F1 0.389</t>
-  </si>
-  <si>
-    <t>X-RGen</t>
-  </si>
-  <si>
-    <t>Cross-region learning</t>
-  </si>
-  <si>
-    <t>HistGen</t>
-  </si>
-  <si>
-    <t>HDGAN</t>
-  </si>
-  <si>
-    <t>MPO</t>
-  </si>
-  <si>
-    <t>Preference optimization</t>
-  </si>
-  <si>
-    <t>GIT-CXR</t>
-  </si>
-  <si>
-    <t>HKRG</t>
-  </si>
-  <si>
-    <t>Clinical F1 0.339</t>
-  </si>
-  <si>
-    <t>MediVLM</t>
-  </si>
-  <si>
-    <t>Severity scoring</t>
-  </si>
-  <si>
-    <t>CLIP-ViT + ClinicalBERT</t>
-  </si>
-  <si>
-    <t>META-CXR</t>
-  </si>
-  <si>
-    <t>Clinical F1 0.428</t>
-  </si>
-  <si>
-    <t>RaDialog</t>
-  </si>
-  <si>
-    <t>Flamingo-CXR</t>
-  </si>
-  <si>
-    <t>RIHA</t>
-  </si>
-  <si>
-    <t>SDLS</t>
-  </si>
-  <si>
-    <t>KERM</t>
-  </si>
-  <si>
-    <t>Hallucination mitigation</t>
-  </si>
-  <si>
-    <t>Clinical F1 0.415</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>CIDEr</t>
-  </si>
-  <si>
-    <t>Clinical Metric</t>
-  </si>
-  <si>
-    <t>CoAttention</t>
-  </si>
-  <si>
-    <t>CheXpert F1</t>
-  </si>
-  <si>
-    <t>Human eval improved</t>
-  </si>
-  <si>
-    <t>Histopathology reports</t>
-  </si>
-  <si>
-    <t>Hierarchical knowledge</t>
-  </si>
-  <si>
-    <t>Clinical F1 0.375</t>
-  </si>
-  <si>
-    <t>F1 0.353</t>
-  </si>
-  <si>
-    <t>GAN + RL</t>
-  </si>
-  <si>
-    <t>F1-micro 0.534</t>
-  </si>
-  <si>
-    <t>Clinical efficacy 39.7</t>
-  </si>
-  <si>
-    <t>CheXpert F1 0.519</t>
-  </si>
-  <si>
-    <t>Hallucination ↓ 37.3%</t>
-  </si>
-  <si>
-    <t>Dataset</t>
-  </si>
-  <si>
-    <t>Main Contribution</t>
-  </si>
-  <si>
-    <t>Key Result</t>
-  </si>
-  <si>
-    <t>CheXpert / MIMIC</t>
-  </si>
-  <si>
-    <t>Contrastive medical VLM</t>
-  </si>
-  <si>
-    <t>59.4% zero-shot accuracy</t>
-  </si>
-  <si>
-    <t>BioViL</t>
-  </si>
-  <si>
-    <t>Biomedical vision-language alignment</t>
-  </si>
-  <si>
-    <t>Improved phrase grounding</t>
-  </si>
-  <si>
-    <t>BLIP</t>
-  </si>
-  <si>
-    <t>COCO / Web-scale</t>
-  </si>
-  <si>
-    <t>Unified VLP framework</t>
-  </si>
-  <si>
-    <t>CIDEr 129.7</t>
-  </si>
-  <si>
-    <t>CLIP</t>
-  </si>
-  <si>
-    <t>Web-scale</t>
-  </si>
-  <si>
-    <t>Contrastive image-text learning</t>
-  </si>
-  <si>
-    <t>76.2% ImageNet zero-shot</t>
-  </si>
-  <si>
-    <t>ClinicalBERT</t>
-  </si>
-  <si>
-    <t>MIMIC-III</t>
-  </si>
-  <si>
-    <t>Clinical text understanding</t>
-  </si>
-  <si>
-    <t>AUROC 0.714</t>
   </si>
   <si>
     <t>Pneumonia classification</t>
@@ -319,7 +319,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,7 +376,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -709,44 +709,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E0D72FE-DC85-4A19-A395-E4AFC5F6F1BB}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="14.28515625" customWidth="1"/>
+    <col min="8" max="8" width="47.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3">
         <v>2018</v>
@@ -764,15 +764,15 @@
         <v>0.32700000000000001</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3">
         <v>2020</v>
@@ -781,24 +781,24 @@
         <v>0.217</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3">
         <v>0.46800000000000003</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3">
         <v>2020</v>
@@ -813,16 +813,16 @@
         <v>0.371</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -839,18 +839,18 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3">
         <v>2024</v>
@@ -865,18 +865,18 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3">
         <v>2024</v>
@@ -894,15 +894,15 @@
         <v>0.42599999999999999</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3">
         <v>2024</v>
@@ -917,18 +917,18 @@
         <v>0.36099999999999999</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G8" s="3">
         <v>0.52300000000000002</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3">
         <v>2024</v>
@@ -943,18 +943,18 @@
         <v>0.34399999999999997</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3">
         <v>2025</v>
@@ -969,16 +969,16 @@
         <v>0.375</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G10" s="5">
         <v>0.61599999999999999</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
@@ -995,18 +995,18 @@
         <v>0.41799999999999998</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B12" s="3">
         <v>2026</v>
@@ -1015,24 +1015,24 @@
         <v>0.218</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" s="3">
         <v>0.42099999999999999</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B13" s="3">
         <v>2026</v>
@@ -1047,13 +1047,13 @@
         <v>0.38800000000000001</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1064,41 +1064,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236AF12A-C64C-4B49-ACC9-3EF7A9BACDA1}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="18.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="18.28515625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="30.33203125" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="30.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3">
         <v>2020</v>
@@ -1113,16 +1113,16 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -1139,18 +1139,18 @@
         <v>0.28699999999999998</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3">
         <v>2023</v>
@@ -1165,18 +1165,18 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3">
         <v>2024</v>
@@ -1191,18 +1191,18 @@
         <v>0.309</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B6" s="3">
         <v>2024</v>
@@ -1211,24 +1211,24 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3">
         <v>0.28999999999999998</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3">
         <v>2025</v>
@@ -1243,18 +1243,18 @@
         <v>0.312</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3">
         <v>2025</v>
@@ -1263,48 +1263,48 @@
         <v>0.123</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3">
         <v>0.29299999999999998</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3">
         <v>2025</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D9" s="6">
         <v>0.17299999999999999</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G9" s="5">
         <v>0.42599999999999999</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
@@ -1321,117 +1321,117 @@
         <v>0.31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B11" s="3">
         <v>2025</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G11" s="3">
         <v>0.4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B12" s="3">
         <v>2025</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3">
         <v>2026</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B14" s="3">
         <v>2026</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1442,125 +1442,125 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44EDAF90-EB76-4D2F-8586-83492AD5E90F}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="22.109375" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" customWidth="1"/>
-    <col min="4" max="4" width="38.77734375" customWidth="1"/>
-    <col min="5" max="5" width="47.21875" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" customWidth="1"/>
+    <col min="5" max="5" width="47.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B2" s="3">
         <v>2022</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="B3" s="3">
         <v>2023</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="B4" s="3">
         <v>2022</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="B5" s="3">
         <v>2021</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="B6" s="3">
         <v>2020</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="B7" s="3">
         <v>2017</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>74</v>
@@ -1569,7 +1569,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>76</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>2021</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>77</v>
@@ -1586,7 +1586,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>79</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>2019</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>80</v>
@@ -1603,7 +1603,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>82</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>2025</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>83</v>
@@ -1620,7 +1620,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
         <v>85</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>2024</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>86</v>
@@ -1646,9 +1646,5 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3808D55-6330-4A94-A10B-E4E2B2E1DA2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3808D55-6330-4A94-A10B-E4E2B2E1DA2A}"/>
 </file>